--- a/outputs/resultats/td/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/td/2025_t2_vs_2025_t1/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -573,14 +573,14 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Les attentes de la Banque à l’égard des niveaux de liquidités s’appuient sur les hypothèses de la Banque à l’égard de certains facteurs, notamment la croissance des produits, les plans stratégiques, le rythme des rachats d’actions dans le cadre de l’offre publique de rachat dans le cours normal des activités de la Banque (laquelle est assujettie aux prévisions financières et aux exigences en matière de fonds propres). Les hypothèses de la Banque sont assujetties à des incertitudes inhérentes et peuvent varier en fonction de plusieurs facteurs dépendants et indépendants de la volonté de la Banque, y compris les conditions générales du marché, les perspectives économiques et les enjeux géopolitiques. Se reporter à la section « Facteurs de risque qui pourraient avoir une incidence sur les résultats futurs » du présent document pour plus de renseignements sur les risques et les incertitudes susceptibles d’influer sur les résultats futurs de la Banque.</t>
+          <t>Les attentes de la Banque à l’égard des niveaux de liquidités s’appuient sur les hypothèses de la Banque à l’égard de certains facteurs, notamment la croissance des produits, les plans stratégiques, le rythme des rachats d’actions dans le cadre de l’offre publique de rachat dans le cours normal des activités de la Banque (laquelle est assujettie aux prévisions financières et aux exigences en matière de fonds propres). Les hypothèses de la Banque sont assujetties à des incertitudes inhérentes et peuvent varier en fonction de plusieurs facteurs dépendants et indépendants de la volonté de la Banque, y compris les conditions générales du marché, les perspectives économiques et les enjeux géopolitiques. Se reporter à la section « Facteurs de risque qui pourraient avoir une incidence sur les résultats futurs » du présent document pour plus de renseignements sur les risques et les incertitudes susceptibles</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n-15 a été ajoutée dans le tableau des mesures de liquidité réglementaire de la Banque au T2 2025.
-Cette note précise les attentes de la Banque en matière de niveaux de liquidités, en se basant sur des hypothèses concernant divers facteurs, tels que la croissance des produits et les plans stratégiques. Elle mentionne également que ces hypothèses sont sujettes à des incertitudes et peuvent varier en fonction de facteurs indépendants de la volonté de la Banque. Cette information est cruciale pour comprendre comment la Banque anticipe et gère ses niveaux de liquidité, ce qui est essentiel pour les investisseurs et les régulateurs.
-Il s'agit d'une mise à jour structurante qui pourrait refléter un ajustement dans la stratégie de gestion de la liquidité de la Banque. L'analyste devrait confirmer que cette nouvelle note est cohérente avec les autres divulgations de liquidité et évaluer son impact potentiel sur les ratios de liquidité réglementaires.</t>
+          <t>La note de bas de page n°15 a été ajoutée dans le tableau des mesures de liquidité réglementaires et notes explicatives au T2 2025. Cette note détaille les attentes de la Banque concernant les niveaux de liquidités, en se basant sur des hypothèses liées à divers facteurs économiques et stratégiques.
+L'ajout de cette note est significatif car il clarifie les hypothèses sous-jacentes aux prévisions de liquidité de la Banque, ce qui est crucial pour l'évaluation des risques de liquidité. Les hypothèses mentionnées, telles que la croissance des produits et les plans stratégiques, sont essentielles pour comprendre comment la Banque anticipe ses besoins en liquidités et ses stratégies de gestion des risques. Cela est particulièrement pertinent dans le contexte des exigences de Bâle III et des lignes directrices du BSIF, qui imposent des normes strictes en matière de gestion des liquidités.
+Il s'agit d'une mise à jour structurante qui améliore la transparence des informations fournies aux parties prenantes. L'analyste devrait confirmer que cette nouvelle divulgation est cohérente avec les autres sections du rapport et s'assurer que les hypothèses sont bien alignées avec les prévisions financières et les exigences réglementaires.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -589,21 +589,9 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-19T00:10:00.085773+00:00</t>
-        </is>
-      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -628,25 +616,29 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Renommage</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Les attentes de la Banque à l’égard des niveaux de liquidités s’appuient sur les hypothèses de la Banque à l’égard de certains facteurs, notamment la croissance des produits, les plans stratégiques, le rythme des rachats d’actions dans le cadre de l’offre publique de rachat dans le cours normal des activités de la Banque (laquelle est assujettie à l’approbation des organismes de réglementation, aux prévisions financières et aux exigences en matière de fonds propres). Les hypothèses de la Banque sont assujetties à des incertitudes inhérentes et peuvent varier en fonction de plusieurs facteurs dépendants et indépendants de la volonté de la Banque, y compris les conditions générales du marché, les perspectives économiques et les enjeux géopolitiques. Se reporter à la section « Facteurs de risque qui pourraient avoir une incidence sur les résultats futurs » du présent document pour plus de renseignements sur les principaux facteurs de risque et incertitudes qui peuvent faire en sorte que les résultats réels diffèrent sensiblement des attentes.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+          <t>RATIO DE LIQUIDITÉ À LONG TERME</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>RATIO DE LIQUIDITÉ À LONG TERME (NSFR)</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n-13 a été supprimée du tableau des ratios de liquidité à court terme moyen au T1 2025.
-Cette note détaillait les attentes de la Banque concernant les niveaux de liquidités, en soulignant l'importance des hypothèses de croissance des produits et des plans stratégiques. Elle mentionnait également que ces hypothèses étaient soumises à l'approbation des organismes de réglementation, ce qui est une information cruciale pour comprendre les contraintes réglementaires auxquelles la Banque est soumise.
-La suppression de cette note pourrait indiquer un changement dans la manière dont la Banque communique ses attentes en matière de liquidité ou une révision de ses hypothèses stratégiques. L'analyste devrait investiguer si cette suppression est compensée par d'autres divulgations ou si elle reflète un changement dans la stratégie de gestion de la liquidité.</t>
+          <t>L'indicateur "RATIO DE LIQUIDITÉ À LONG TERME" a été renommé en "RATIO DE LIQUIDITÉ À LONG TERME (NSFR)" dans le tableau des mesures de liquidité réglementaires et notes explicatives au T2 2025, alors qu'il était simplement intitulé "RATIO DE LIQUIDITÉ À LONG TERME" au T1 2025.
+Ce changement de nom indique une clarification importante concernant le type de ratio de liquidité à long terme présenté. Le NSFR (Net Stable Funding Ratio) est une mesure clé de la stabilité de financement à long terme, exigée par les normes de Bâle III. Cette clarification est cruciale pour les parties prenantes, car elle précise que le ratio présenté est conforme aux exigences réglementaires internationales en matière de liquidité.
+Il s'agit d'une mise à jour structurante qui améliore la transparence et la précision des informations fournies. L'analyste devrait confirmer que cette clarification est cohérente avec les autres divulgations de liquidité dans le rapport et s'assurer que les calculs sous-jacents respectent les méthodologies NSFR prescrites.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -655,9 +647,21 @@
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23T09:36:50.293551+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -667,17 +671,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ACTIFS GREVÉS ET ACTIFS NON GREVÉS</t>
+          <t>(sans titre)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -687,24 +691,20 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Les autres actifs comprennent la participation dans Schwab, le goodwill, les autres immobilisations incorporelles, les terrains, bâtiments, matériel et mobilier, autres actifs amortissables et actifs au titre de droits d’utilisation, les actifs d’impôt différé, les montants à recevoir des courtiers et des clients et les autres actifs du bilan qui ne sont pas présentés dans les catégories ci-dessus.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Les autres actifs comprennent le goodwill, les autres immobilisations incorporelles, les terrains, bâtiments, matériel et mobilier, autres actifs amortissables et actifs au titre de droits d’utilisation, les actifs d’impôt différé, les montants à recevoir des courtiers et des clients et les autres actifs du bilan qui ne sont pas présentés dans les catégories ci-dessus.</t>
-        </is>
-      </c>
+          <t>Les attentes de la Banque à l’égard des niveaux de liquidités s’appuient sur les hypothèses de la Banque à l’égard de certains facteurs, notamment la croissance des produits, les plans stratégiques, le rythme des rachats d’actions dans le cadre de l’offre publique de rachat dans le cours normal des activités de la Banque (laquelle est assujettie à l’approbation des organismes de réglementation, aux prévisions financières et aux exigences en matière de fonds propres). Les hypothèses de la Banque sont assujetties à des incertitudes inhérentes et peuvent varier en fonction de plusieurs facteurs dépendants et indépendants de la volonté de la Banque, y compris les conditions générales du marché, les perspectives économiques et les enjeux géopolitiques. Se reporter à la section « Facteurs de risque qui pourraient avoir une incidence sur les résultats futurs » du présent document pour plus de renseignements sur certains facteurs sous-jacents aux attentes de la Banque.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n-5 a été modifiée dans le tableau des actifs grevés et non grevés, avec la suppression de la mention de la 'participation dans Schwab'. Cette modification pourrait indiquer un changement dans la composition des actifs ou une révision de la présentation des actifs.
-L'impact métier de cette suppression est potentiellement significatif, car elle pourrait refléter un changement dans la structure des actifs de la banque. Cela pourrait avoir des implications sur les ratios prudentiels ou les exigences de divulgation, notamment si la participation dans Schwab représentait une part importante des actifs. Les régulateurs, tels que le BSIF, pourraient exiger des explications supplémentaires si cette modification affecte les ratios de capital ou de liquidité.
-Il s'agit d'un changement structurel qui pourrait nécessiter une investigation plus approfondie. L'analyste devrait vérifier si cette suppression est liée à une vente, une réévaluation ou une autre transaction significative, et s'assurer que les divulgations sont cohérentes avec les autres sections du rapport.</t>
+          <t>La note de bas de page n°13 a été supprimée du tableau des mesures de liquidité réglementaires et notes explicatives au T2 2025. Cette note, présente au T1 2025, détaillait les attentes de la Banque concernant les niveaux de liquidités, en se basant sur des hypothèses liées à divers facteurs économiques et stratégiques.
+La suppression de cette note peut avoir un impact sur la transparence des informations fournies aux parties prenantes, car elle retirait des détails importants sur les hypothèses de liquidité de la Banque. Ces hypothèses sont essentielles pour comprendre comment la Banque anticipe ses besoins en liquidités et ses stratégies de gestion des risques, en lien avec les exigences de Bâle III et les lignes directrices du BSIF.
+Il s'agit d'une mise à jour structurante qui pourrait affecter la compréhension des stratégies de liquidité de la Banque. L'analyste devrait investiguer les raisons de cette suppression et s'assurer que les informations essentielles sont toujours disponibles ailleurs dans le rapport ou dans d'autres communications de la Banque.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -725,17 +725,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DURÉE CONTRACTUELLE RESTANTE</t>
+          <t>ACTIFS GREVÉS ET ACTIFS NON GREVÉS</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -750,19 +750,19 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Comprennent 75 milliards de dollars d’obligations sécurisées, dont une tranche de 2 milliards de dollars comporte une durée contractuelle restante de « plus de 1 à 3 mois », une tranche de 10 milliards de dollars comporte une durée contractuelle restante de « plus de 3 mois à 6 mois », une tranche de 22 milliards de dollars comporte une durée contractuelle restante de « plus de 1 an à 2 ans », une tranche de 33 milliards de dollars comporte une durée contractuelle restante de « plus de 2 à 5 ans » et une tranche de 8 milliards de dollars comporte une durée contractuelle restante de « plus de 5 ans ».</t>
+          <t>Les autres actifs comprennent la participation dans Schwab, le goodwill, les autres immobilisations incorporelles, les terrains, bâtiments, matériel et mobilier, autres actifs amortissables et actifs au titre de droits d’utilisation, les actifs d’impôt différé, les montants à recevoir des courtiers et des clients et les autres actifs du bilan qui ne sont pas présentés dans les catégories ci-dessus.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Comprennent 74 milliards de dollars d’obligations sécurisées, dont une tranche de 10 milliards de dollars comporte une durée contractuelle restante de « plus de 1 à 3 mois », une tranche de 10 milliards de dollars comporte une durée contractuelle restante de « plus de 9 mois à 1 an », une tranche de 22 milliards de dollars comporte une durée contractuelle restante de « plus de 1 an à 2 ans », une tranche de 26 milliards de dollars comporte une durée contractuelle restante de « plus de 2 à 5 ans » et une tranche de 6 milliards de dollars comporte une durée contractuelle restante de « plus de 5 ans ».</t>
+          <t>Les autres actifs comprennent le goodwill, les autres immobilisations incorporelles, les terrains, bâtiments, matériel et mobilier, autres actifs amortissables et actifs au titre de droits d’utilisation, les actifs d’impôt différé, les montants à recevoir des courtiers et des clients et les autres actifs du bilan qui ne sont pas présentés dans les catégories ci-dessus.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n°5 a subi une révision significative dans le tableau de la durée contractuelle restante. Le texte précédent mentionnait 75 milliards de dollars d'obligations sécurisées avec des répartitions spécifiques par tranche de durée. Le texte actuel indique 74 milliards de dollars, avec des modifications dans les tranches de durée, notamment l'ajout d'une tranche de « plus de 9 mois à 1 an » et des ajustements dans les montants des autres tranches.
-Ce changement a un impact direct sur la compréhension des obligations sécurisées de la banque, ce qui peut affecter les ratios de liquidité et de financement à long terme. Les obligations sécurisées sont souvent utilisées pour répondre aux exigences de Bâle III en matière de liquidité, et toute modification de leur répartition peut influencer les calculs des ratios de couverture de liquidité (LCR) et de financement stable net (NSFR).
-Il s'agit d'une mise à jour structurelle importante qui pourrait refléter un changement dans la stratégie de financement de la banque. L'analyste devrait confirmer la cohérence de ces chiffres avec les autres sections du rapport financier et s'assurer que les ajustements sont correctement intégrés dans les calculs des ratios prudentiels.</t>
+          <t>La note de bas de page n°5 a été modifiée par la suppression de la mention de la participation dans Schwab. Cette note se trouve dans le tableau des actifs grevés et non grevés, et décrit les autres actifs de la banque.
+L'impact de cette suppression est plus significatif, car elle pourrait indiquer un changement dans la structure des actifs de la banque. La participation dans Schwab étant un élément potentiellement important du portefeuille d'actifs, sa suppression de la note pourrait refléter une vente ou une réévaluation stratégique. Cela pourrait avoir des implications sur les ratios de fonds propres ou sur la stratégie de gestion des actifs de la banque, en lien avec les exigences de Bâle III ou les directives du BSIF.
+Il s'agit d'un changement structurel qui mérite une investigation plus approfondie. L'analyste devrait vérifier si cette suppression est liée à une transaction récente ou à une réorganisation des actifs, et évaluer son impact sur les autres tableaux financiers du rapport.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -771,9 +771,21 @@
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23T09:38:13.252037+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -783,17 +795,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FINANCEMENT DE GROS</t>
+          <t>DURÉE CONTRACTUELLE RESTANTE</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -808,19 +820,19 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Comprennent la dette de premier rang qui est assujettie à une conversion au titre du régime de recapitalisation interne des banques. Excluent des billets structurés d’un montant de 4,0 milliards de dollars qui sont assujettis à une conversion au titre du régime de recapitalisation interne des banques (4,4 milliards de dollars au 31 octobre 2024).</t>
+          <t>Comprennent 75 milliards de dollars d’obligations sécurisées, dont une tranche de 2 milliards de dollars comporte une durée contractuelle restante de « plus de 1 à 3 mois », une tranche de 10 milliards de dollars comporte une durée contractuelle restante de « plus de 3 mois à 6 mois », une tranche de 22 milliards de dollars comporte une durée contractuelle restante de « plus de 1 an à 2 ans », une tranche de 33 milliards de dollars comporte une durée contractuelle restante de « plus de 2 à 5 ans » et une tranche de 8 milliards de dollars comporte une durée contractuelle restante de « plus de 5 ans ».</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Comprennent la dette de premier rang qui est assujettie à une conversion au titre du régime de recapitalisation interne des banques. Excluent des billets structurés d’un montant de 3,7 milliards de dollars qui sont assujettis à une conversion au titre du régime de recapitalisation interne des banques (4,4 milliards de dollars au 31 octobre 2024).</t>
+          <t>Comprennent 74 milliards de dollars d’obligations sécurisées, dont une tranche de 10 milliards de dollars comporte une durée contractuelle restante de « plus de 1 à 3 mois », une tranche de 10 milliards de dollars comporte une durée contractuelle restante de « plus de 9 mois à 1 an », une tranche de 22 milliards de dollars comporte une durée contractuelle restante de « plus de 1 an à 2 ans », une tranche de 26 milliards de dollars comporte une durée contractuelle restante de « plus de 2 à 5 ans » et une tranche de 6 milliards de dollars comporte une durée contractuelle restante de « plus de 5 ans ».</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n-4 a été modifiée dans le tableau du financement de gros. Le texte a été ajusté pour refléter une modification du montant des billets structurés exclus de la conversion au titre du régime de recapitalisation interne des banques, passant de 4,0 milliards de dollars à 3,7 milliards de dollars.
-Ce changement a un impact direct sur la divulgation des engagements financiers de la banque, en particulier en ce qui concerne la gestion des risques liés à la recapitalisation interne. La réduction du montant des billets structurés exclus pourrait indiquer une réévaluation des risques ou une modification des stratégies de financement. Cela pourrait également avoir des implications sur les ratios de capital réglementaire, notamment ceux liés à Bâle III, qui exigent une transparence accrue sur les instruments de dette pouvant être convertis en capital en cas de crise.
-Il s'agit d'une mise à jour significative qui pourrait refléter un ajustement stratégique ou une réponse à des exigences réglementaires. L'analyste devrait confirmer la raison de cette modification et s'assurer qu'elle est cohérente avec les autres divulgations financières et les stratégies de gestion des risques de la banque.</t>
+          <t>La note de bas de page n°5 a subi une révision significative dans le tableau de la durée contractuelle restante. Le montant total des obligations sécurisées a été ajusté de 75 milliards de dollars à 74 milliards de dollars, et les tranches ont été redistribuées avec des durées contractuelles différentes, notamment l'ajout d'une tranche de 10 milliards de dollars pour la période de « plus de 9 mois à 1 an » et des ajustements dans les autres tranches.
+Ce changement a un impact structurel important car il modifie la répartition des obligations sécurisées par durée, ce qui peut affecter l'analyse de la liquidité et du risque de taux d'intérêt de la banque. Les obligations sécurisées sont souvent utilisées pour garantir des financements à long terme, et leur répartition par échéance est cruciale pour la gestion des risques de liquidité et de taux. Selon les normes de Bâle III, la gestion des échéances est essentielle pour le calcul des ratios de liquidité, tels que le ratio de liquidité à court terme (LCR) et le ratio de financement stable net (NSFR).
+Il s'agit d'une mise à jour méthodologique qui nécessite une attention particulière. L'analyste devrait confirmer que ces ajustements sont cohérents avec les autres divulgations financières et s'assurer que les changements dans la répartition des échéances sont correctement intégrés dans les modèles de gestion des risques de la banque. Une vérification supplémentaire pourrait être nécessaire pour garantir que ces ajustements ne compromettent pas la conformité réglementaire.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -841,7 +853,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-19T00:10:06.423784+00:00</t>
+          <t>2026-04-23T09:37:32.461532+00:00</t>
         </is>
       </c>
     </row>
@@ -878,19 +890,19 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Comprend les dépôts à échéance déterminée d’institutions autres que des banques (non garantis) de 17,0 milliards de dollars (17,3 milliards de dollars au 31 octobre 2024) et les autres dépôts n’ont aucune échéance.</t>
+          <t>Comprennent la dette de premier rang qui est assujettie à une conversion au titre du régime de recapitalisation interne des banques. Excluent des billets structurés d’un montant de 4,0 milliards de dollars qui sont assujettis à une conversion au titre du régime de recapitalisation interne des banques (4,4 milliards de dollars au 31 octobre 2024).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Comprend les dépôts à échéance déterminée d’institutions autres que des banques (non garantis) de 19,8 milliards de dollars (17,3 milliards de dollars au 31 octobre 2024) et les autres dépôts n’ont aucune échéance.</t>
+          <t>Comprennent la dette de premier rang qui est assujettie à une conversion au titre du régime de recapitalisation interne des banques. Excluent des billets structurés d’un montant de 3,7 milliards de dollars qui sont assujettis à une conversion au titre du régime de recapitalisation interne des banques (4,4 milliards de dollars au 31 octobre 2024).</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n-6 a été modifiée dans le tableau du financement de gros. Le texte a été ajusté pour refléter une augmentation du montant des dépôts à échéance déterminée d’institutions autres que des banques, passant de 17,0 milliards de dollars à 19,8 milliards de dollars.
-Cette modification indique une augmentation significative des engagements financiers de la banque envers des institutions non bancaires. Cela peut avoir des implications sur la liquidité et la gestion des risques de la banque, car une augmentation des dépôts non garantis peut affecter la stabilité financière en période de stress. De plus, cette modification pourrait influencer les ratios de liquidité réglementaires, tels que le ratio de liquidité à court terme (LCR) et le ratio de financement stable net (NSFR), qui sont des exigences clés sous Bâle III.
-Il s'agit d'une mise à jour importante qui pourrait refléter une stratégie de financement modifiée ou une réponse à des conditions de marché changeantes. L'analyste devrait examiner les raisons de cette augmentation et évaluer son impact sur la gestion des risques et la conformité réglementaire de la banque.</t>
+          <t>La note de bas de page n°4 a été modifiée dans le tableau du financement de gros. Le texte a été ajusté pour refléter une modification du montant des billets structurés exclus de la conversion au titre du régime de recapitalisation interne des banques, passant de 4,0 milliards de dollars à 3,7 milliards de dollars.
+Ce changement a un impact direct sur la divulgation des engagements financiers de la banque, en particulier en ce qui concerne la gestion des risques liés aux instruments de dette de premier rang. La réduction du montant des billets structurés exclus pourrait indiquer une réévaluation des risques associés ou une modification des conditions de marché. Cela pourrait également avoir des implications sur les ratios de capital réglementaire, notamment ceux liés à Bâle III, qui exigent une divulgation précise des instruments de dette pouvant être convertis en capital en cas de crise.
+Il s'agit d'une mise à jour importante qui pourrait signaler un changement dans la stratégie de gestion des risques de la banque. L'analyste devrait confirmer la raison de cette modification et s'assurer qu'elle est cohérente avec les autres divulgations financières et les stratégies de gestion des risques de la banque. Une investigation plus approfondie pourrait être nécessaire pour comprendre l'impact complet de ce changement.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -899,9 +911,21 @@
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23T09:37:13.014781+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -911,17 +935,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>NOTATIONS DE CRÉDIT¹</t>
+          <t>FINANCEMENT DE GROS</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -931,20 +955,24 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Comprend les dépôts à échéance déterminée d’institutions autres que des banques (non garantis) de 17,0 milliards de dollars (17,3 milliards de dollars au 31 octobre 2024) et les autres dépôts n’ont aucune échéance.</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Tient compte de l’abaissement des notations de crédit et de la modification des perspectives par DBRS après la fin du trimestre, le 2 mai 2025.</t>
+          <t>Comprend les dépôts à échéance déterminée d’institutions autres que des banques (non garantis) de 19,8 milliards de dollars (17,3 milliards de dollars au 31 octobre 2024) et les autres dépôts n’ont aucune échéance.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n-2 a été ajoutée dans le tableau des notations de crédit au T2 2025.
-Cette note précise que les notations de crédit et les perspectives de DBRS ont été abaissées après la fin du trimestre, le 2 mai 2025. Cela indique un changement potentiel dans la perception du risque de crédit par l'agence de notation, ce qui pourrait avoir des implications sur les coûts de financement et la perception du risque par les investisseurs.
-Il s'agit d'une mise à jour importante qui pourrait affecter les ratios prudentiels et la divulgation réglementaire. L'analyste devrait confirmer l'impact de cette révision sur les autres tableaux de risque de crédit et s'assurer que les ajustements nécessaires ont été effectués dans les rapports financiers.</t>
+          <t>La note de bas de page n°6 a été modifiée dans le tableau du financement de gros. Le texte a été ajusté pour refléter une augmentation du montant des dépôts à échéance déterminée d’institutions autres que des banques, passant de 17,0 milliards de dollars à 19,8 milliards de dollars.
+Cette modification a des implications significatives pour la gestion de la liquidité et la structure de financement de la banque. Une augmentation de ce type de dépôts peut indiquer une stratégie de financement plus agressive ou une réponse à des conditions de marché changeantes. Cela pourrait également affecter les ratios de liquidité réglementaires, tels que le ratio de liquidité à court terme (LCR) et le ratio de financement stable net (NSFR), qui sont des exigences clés sous Bâle III.
+Il s'agit d'une mise à jour structurelle importante qui pourrait refléter un changement dans la stratégie de financement de la banque. L'analyste devrait confirmer la raison de cette augmentation et s'assurer qu'elle est alignée avec les objectifs stratégiques de la banque. Une vérification plus approfondie pourrait être nécessaire pour évaluer l'impact de ce changement sur la stabilité financière de l'institution.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -965,17 +993,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SENSIBILITÉ AU RISQUE DE TAUX D’INTÉRÊT STRUCTUREL – MESURES</t>
+          <t>NOTATIONS DE CRÉDIT¹</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -985,24 +1013,20 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Représente l’exposition des produits d’intérêts nets au cours des douze mois suivant un choc immédiat et soutenu des taux d’intérêt.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Représente l’exposition des produits d’intérêts nets au cours des douze mois suivant un choc immédiat et soutenu des taux d’intérêt et peut comprendre des ajustements au titre d’éléments non récurrents.</t>
+          <t>Tient compte de l’abaissement des notations de crédit et de la modification des perspectives par DBRS après la fin du trimestre, le 2 mai 2025.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n°1 a été modifiée dans le tableau de la sensibilité au risque de taux d’intérêt structurel. Le texte initial décrivait l’exposition des produits d’intérêts nets sur douze mois après un choc de taux d’intérêt. La version révisée ajoute que cette exposition peut inclure des ajustements pour des éléments non récurrents.
-Cette modification a un impact significatif sur la compréhension des résultats financiers projetés. En intégrant la possibilité d’ajustements pour des éléments non récurrents, la banque indique que les résultats pourraient être influencés par des événements exceptionnels ou des ajustements ponctuels. Cela peut affecter la transparence et la comparabilité des résultats financiers, ce qui est crucial pour les investisseurs et les régulateurs. Selon les normes IFRS et les recommandations du BSIF, toute modification de la méthodologie de calcul des expositions doit être clairement divulguée et justifiée.
-Il s'agit d'un changement méthodologique important. L'analyste devrait confirmer que cette nouvelle approche est cohérente avec les autres divulgations de risque de taux d’intérêt dans le rapport et s'assurer que les ajustements non récurrents sont correctement documentés et justifiés. Une investigation plus approfondie est recommandée pour évaluer l'impact potentiel sur les ratios prudentiels et la conformité réglementaire.</t>
+          <t>La note de bas de page n-2 a été ajoutée dans le tableau des notations de crédit au T2 2025.
+Cette note précise que les notations de crédit et les perspectives ont été abaissées par DBRS après la fin du trimestre, le 2 mai 2025. Cela indique un changement potentiel dans l'évaluation du risque de crédit de la Banque par une agence de notation, ce qui peut avoir des implications sur la perception du marché et les coûts de financement.
+Il s'agit d'une divulgation importante qui pourrait affecter la stratégie de gestion des risques de la Banque. L'analyste devrait confirmer l'impact de cette révision sur les ratios prudentiels et la conformité aux exigences réglementaires, notamment celles de Bâle III et du BSIF.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1023,17 +1047,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE</t>
+          <t>SENSIBILITÉ AU RISQUE DE TAUX D’INTÉRÊT STRUCTUREL – MESURES</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1043,20 +1067,24 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Représente l’exposition des produits d’intérêts nets au cours des douze mois suivant un choc immédiat et soutenu des taux d’intérêt.</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Comprennent les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.</t>
+          <t>Représente l’exposition des produits d’intérêts nets au cours des douze mois suivant un choc immédiat et soutenu des taux d’intérêt et peut comprendre des ajustements au titre d’éléments non récurrents.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n°2 a été ajoutée dans le tableau des actifs liquides moyens par type et par monnaie au T2 2025. Cette note précise que les actifs liquides comprennent désormais les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.
-L'ajout de cette note indique une inclusion explicite de ces titres dans le calcul des actifs liquides. Cela peut avoir un impact significatif sur la gestion des risques de liquidité de la banque, car ces titres sont souvent utilisés pour améliorer la liquidité et diversifier les actifs. De plus, cette inclusion pourrait influencer les ratios de liquidité réglementaires, tels que le LCR (Liquidity Coverage Ratio) sous Bâle III, en augmentant potentiellement le montant des actifs liquides éligibles.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette inclusion est correctement intégrée dans les calculs de liquidité et que sa classification est conforme aux normes réglementaires en vigueur. Une vérification de la cohérence avec les autres tableaux de liquidité du rapport est également recommandée.</t>
+          <t>La note de bas de page n°1 a été modifiée dans le tableau de la sensibilité au risque de taux d’intérêt structurel. Le texte initial décrivait l’exposition des produits d’intérêts nets sur douze mois après un choc de taux d’intérêt. La version révisée ajoute que cette exposition peut inclure des ajustements pour des éléments non récurrents.
+Cette modification a un impact significatif sur l’interprétation des résultats financiers. En incluant la possibilité d’ajustements pour des éléments non récurrents, la banque introduit une variabilité potentielle dans les résultats qui pourrait affecter les ratios de sensibilité au risque de taux d’intérêt. Cela pourrait avoir des implications sur la manière dont les investisseurs et les régulateurs perçoivent la stabilité financière de l’institution, notamment en lien avec les exigences de Bâle III sur la gestion du risque de taux d’intérêt.
+Il s’agit d’un changement méthodologique important. L’analyste devrait confirmer que cette nouvelle approche est cohérente avec les autres divulgations de risque de taux d’intérêt dans le rapport et s’assurer que les ajustements pour éléments non récurrents sont correctement documentés et justifiés. Une investigation plus approfondie est recommandée pour évaluer l’impact de ces ajustements sur les résultats financiers.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1065,9 +1093,21 @@
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23T09:38:07.654009+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1097,20 +1137,20 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Obligations du gouvernement du Canada</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Autres titres de créance</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Obligations du gouvernement du Canada" a été retiré du tableau de synthèse des actifs liquides moyens par type et par monnaie au T2 2025, alors qu'il était présent au T1 2025.
-Cette suppression pourrait indiquer un changement dans la manière dont la banque classe ou gère ses obligations gouvernementales. Cela peut avoir des implications sur la gestion des risques de liquidité et de taux d'intérêt, car les obligations gouvernementales sont souvent considérées comme des actifs liquides sûrs. La suppression de cet indicateur pourrait également affecter la transparence des rapports financiers et la conformité aux exigences de divulgation réglementaires.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait enquêter pour comprendre la raison de cette suppression et s'assurer que les obligations gouvernementales sont toujours correctement prises en compte dans les calculs de liquidité et de capital.</t>
+          <t>L'indicateur "Autres titres de créance" a été ajouté dans le tableau de synthèse des actifs liquides moyens par type et par monnaie au T2 2025, alors qu'il était absent au T1 2025.
+Cet ajout pourrait indiquer une nouvelle catégorie d'actifs liquides que la banque a commencé à inclure dans ses rapports. Cela peut refléter un changement dans la stratégie de gestion des actifs ou une réponse à des exigences réglementaires accrues concernant la transparence des actifs liquides. Les lignes directrices de Bâle III et les exigences du BSIF en matière de liquidité pourraient être des facteurs influençant cette inclusion.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette nouvelle catégorie est correctement intégrée dans les calculs de liquidité et vérifier si des ajustements similaires apparaissent dans d'autres sections du rapport.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1131,7 +1171,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2026-04-19T00:09:21.360896+00:00</t>
+          <t>2026-04-23T09:36:37.996258+00:00</t>
         </is>
       </c>
     </row>
@@ -1163,20 +1203,20 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Autres titres</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation" a été retiré du tableau de synthèse des actifs liquides moyens par type et par monnaie au T2 2025, alors qu'il était présent au T1 2025.
-Cette suppression pourrait refléter un changement dans la composition des actifs liquides de la banque, potentiellement en raison de modifications réglementaires ou de stratégies de gestion des risques. Les titres adossés à des créances hypothécaires sont souvent utilisés pour gérer les risques de liquidité et de crédit, et leur absence pourrait indiquer un changement significatif dans la stratégie de gestion des actifs de la banque.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait confirmer que cette suppression est conforme aux politiques internes de gestion des risques et aux exigences réglementaires, et évaluer l'impact potentiel sur les ratios de liquidité et de capital.</t>
+          <t>L'indicateur "Autres titres" a été ajouté dans le tableau de synthèse des actifs liquides moyens par type et par monnaie au T2 2025, alors qu'il était absent au T1 2025.
+Cet ajout pourrait signaler une diversification des actifs liquides détenus par la banque, potentiellement en réponse à des changements de marché ou à des directives réglementaires. La diversification des actifs est souvent encouragée pour améliorer la résilience financière et répondre aux exigences de liquidité, telles que celles définies par Bâle III.
+Il s'agit d'une mise à jour structurelle significative. L'analyste devrait examiner si cette nouvelle catégorie d'actifs est alignée avec les stratégies de gestion des risques de la banque et s'assurer que les rapports de liquidité sont cohérents avec cette nouvelle inclusion.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1212,25 +1252,25 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Obligations de gouvernements provinciaux, d’entités du secteur public et de banques multilatérales de développement</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Comprennent les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Obligations de gouvernements provinciaux, d’entités du secteur public et de banques multilatérales de développement" a été retiré du tableau de synthèse des actifs liquides moyens par type et par monnaie au T2 2025, alors qu'il était présent au T1 2025.
-Cette suppression pourrait indiquer une réorganisation des catégories d'actifs liquides, potentiellement pour simplifier la présentation ou en réponse à des changements dans la composition des actifs. Les obligations de gouvernements provinciaux et d'entités publiques sont souvent considérées comme des actifs liquides importants, et leur retrait pourrait avoir des implications sur la gestion des risques de liquidité et de crédit.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait vérifier que cette suppression est justifiée par des changements dans la stratégie de gestion des actifs ou par des exigences réglementaires, et s'assurer que les obligations concernées sont toujours correctement prises en compte dans les rapports financiers.</t>
+          <t>La note de bas de page n°2 a été ajoutée dans le tableau des actifs liquides moyens par type et par monnaie au T2 2025. Cette note précise que les actifs liquides comprennent désormais les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.
+L'ajout de cette note indique une clarification ou une mise à jour de la composition des actifs liquides rapportés par la banque. Cela peut refléter un ajustement dans la manière dont ces actifs sont classifiés ou une réponse à des exigences réglementaires concernant la transparence et la divulgation des actifs liquides. Les directives de Bâle III et les exigences du BSIF en matière de liquidité pourraient influencer cette inclusion.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette nouvelle inclusion est correctement intégrée dans les calculs de liquidité et vérifier si des ajustements similaires apparaissent dans d'autres sections du rapport.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1251,17 +1291,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1271,20 +1311,20 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Autres titres de créance</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Obligations du gouvernement du Canada</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Autres titres de créance" a été ajouté dans le tableau de synthèse des actifs liquides au T2 2025, alors qu'il était absent au T1 2025.
-Cet ajout pourrait refléter une nouvelle catégorie de titres de créance que la banque a commencé à inclure dans ses rapports. Cela peut avoir des implications sur la manière dont la banque gère et rapporte ses actifs liquides, potentiellement en réponse à des changements réglementaires ou à une réévaluation interne de la classification des actifs.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait confirmer que cette nouvelle catégorie est correctement intégrée dans les calculs globaux des actifs liquides et vérifier si des explications supplémentaires sont fournies dans le rapport pour justifier cette inclusion.</t>
+          <t>L'indicateur "Obligations du gouvernement du Canada" a été supprimé du tableau de synthèse des actifs liquides moyens par type et par monnaie au T2 2025, alors qu'il était présent au T1 2025.
+Cette suppression pourrait indiquer une consolidation des catégories d'obligations dans une catégorie plus large, comme "Obligations du gouvernement, d’organismes fédéraux, d’entités du secteur public et de banques multilatérales de développement". Cela peut refléter un changement dans la manière dont la banque regroupe et rapporte ses actifs, potentiellement pour simplifier la présentation ou pour répondre à des exigences de divulgation plus globales.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier si cette consolidation est conforme aux pratiques de reporting standard et s'assurer que les informations sur les obligations spécifiques sont toujours disponibles ailleurs dans le rapport.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1293,21 +1333,9 @@
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-19T00:08:47.750807+00:00</t>
-        </is>
-      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1317,17 +1345,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1337,20 +1365,20 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Autres titres</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Autres titres" a été ajouté dans le tableau de synthèse des actifs liquides au T2 2025, alors qu'il était absent au T1 2025.
-Cet ajout pourrait indiquer une nouvelle classification ou une réorganisation des actifs liquides de la banque. Cela peut être dû à des changements dans la stratégie d'investissement ou à des ajustements pour se conformer à de nouvelles normes comptables ou réglementaires.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait examiner si cette nouvelle catégorie est alignée avec les autres sections du rapport et s'assurer que les définitions et les méthodologies de calcul sont cohérentes.</t>
+          <t>L'indicateur "Titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation" a été supprimé du tableau de synthèse des actifs liquides moyens par type et par monnaie au T2 2025, alors qu'il était présent au T1 2025.
+Cette suppression pourrait indiquer une consolidation ou un changement dans la manière dont ces titres sont classés ou rapportés. Cela peut être dû à une réévaluation de leur classification en tant qu'actifs liquides ou à une modification des exigences de divulgation réglementaire.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette suppression n'affecte pas la transparence des rapports et que les informations pertinentes sont toujours disponibles dans d'autres sections du rapport.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1371,40 +1399,40 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Comprennent les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Obligations de gouvernements provinciaux, d’entités du secteur public et de banques multilatérales de développement</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n°2 a été ajoutée dans le tableau des actifs liquides au T2 2025. Cette note précise que les actifs liquides comprennent désormais les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.
-L'ajout de cette note indique une clarification ou une extension de la définition des actifs liquides. Cela peut avoir des implications sur la manière dont la banque évalue et rapporte ses actifs liquides, potentiellement en réponse à des changements réglementaires ou à une réévaluation interne de la classification des actifs. Cette inclusion pourrait être liée aux exigences de Bâle III concernant la liquidité et la gestion des risques, notamment en ce qui concerne le ratio de liquidité à court terme (LCR).
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait confirmer que cette nouvelle inclusion est correctement intégrée dans les calculs globaux des actifs liquides et vérifier si des explications supplémentaires sont fournies dans le rapport pour justifier cette inclusion.</t>
+          <t>L'indicateur "Obligations de gouvernements provinciaux, d’entités du secteur public et de banques multilatérales de développement" a été supprimé du tableau de synthèse des actifs liquides moyens par type et par monnaie au T2 2025, alors qu'il était présent au T1 2025.
+Cette suppression pourrait être le résultat d'une consolidation dans une catégorie plus large, ce qui pourrait simplifier la présentation des actifs liquides ou répondre à des exigences de divulgation plus globales. Cela peut également refléter un changement dans la stratégie de gestion des actifs de la banque.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait s'assurer que cette consolidation est conforme aux pratiques de reporting standard et que les informations sur ces obligations spécifiques sont toujours disponibles ailleurs dans le rapport.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1425,17 +1453,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1450,15 +1478,15 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Obligations du gouvernement du Canada</t>
+          <t>Obligations de sociétés émettrices</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Obligations du gouvernement du Canada" a été retiré du tableau de synthèse des actifs liquides au T2 2025, alors qu'il était présent au T1 2025.
-Cette suppression semble être le résultat d'une consolidation des catégories d'obligations dans une nouvelle catégorie plus large, "Obligations du gouvernement, d’organismes fédéraux, d’entités du secteur public et de banques multilatérales de développement". Cela peut refléter un changement dans la manière dont la banque regroupe et rapporte ses actifs, potentiellement pour simplifier la présentation ou pour se conformer à de nouvelles exigences réglementaires.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait vérifier que cette consolidation est correctement expliquée dans le rapport et que les impacts sur les ratios de liquidité sont bien compris.</t>
+          <t>L'indicateur "Obligations de sociétés émettrices" a été supprimé du tableau de synthèse des actifs liquides moyens par type et par monnaie au T2 2025, alors qu'il était présent au T1 2025.
+Cette suppression pourrait indiquer une consolidation des catégories d'obligations dans une catégorie plus large ou un changement dans la manière dont ces obligations sont classées. Cela peut être motivé par des exigences de divulgation plus globales ou une simplification de la présentation des actifs liquides.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier que cette consolidation est conforme aux pratiques de reporting standard et s'assurer que les informations sur ces obligations spécifiques sont toujours disponibles ailleurs dans le rapport.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1499,20 +1527,20 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Autres titres de créance</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation" a été retiré du tableau de synthèse des actifs liquides au T2 2025, alors qu'il était présent au T1 2025.
-Cette suppression pourrait indiquer un changement dans la manière dont ces titres sont classifiés ou rapportés. Cela peut être dû à une réévaluation de leur importance relative dans le portefeuille d'actifs liquides de la banque ou à des ajustements pour se conformer à de nouvelles normes comptables ou réglementaires.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait confirmer que cette suppression n'affecte pas négativement la transparence des rapports et vérifier si des explications supplémentaires sont fournies dans le rapport pour justifier cette exclusion.</t>
+          <t>L'indicateur "Autres titres de créance" a été ajouté dans le tableau de synthèse des actifs liquides par type et par monnaie au T2 2025, alors qu'il était absent au T1 2025.
+Cet ajout pourrait refléter une nouvelle catégorie de titres de créance que la banque a commencé à inclure dans ses rapports. Cela peut être lié à une révision de la méthodologie de classification des actifs ou à l'acquisition de nouveaux types d'actifs qui nécessitent une divulgation distincte. Les titres de créance sont souvent soumis à des exigences de divulgation spécifiques en vertu des normes comptables et réglementaires, telles que Bâle III, qui impose des règles strictes sur la liquidité et la qualité des actifs.
+Il s'agit potentiellement d'une mise à jour méthodologique ou d'une nouvelle divulgation. L'analyste devrait confirmer que cette nouvelle catégorie est correctement intégrée dans les calculs de liquidité et qu'elle respecte les exigences réglementaires applicables.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1521,9 +1549,21 @@
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23T09:35:55.816120+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1553,20 +1593,20 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Obligations de gouvernements provinciaux, d’entités du secteur public et de banques multilatérales de développement</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Autres titres</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Obligations de gouvernements provinciaux, d’entités du secteur public et de banques multilatérales de développement" a été retiré du tableau de synthèse des actifs liquides au T2 2025, alors qu'il était présent au T1 2025.
-Cette suppression semble être le résultat d'une consolidation des catégories d'obligations dans une nouvelle catégorie plus large, "Obligations du gouvernement, d’organismes fédéraux, d’entités du secteur public et de banques multilatérales de développement". Cela peut refléter un changement dans la manière dont la banque regroupe et rapporte ses actifs, potentiellement pour simplifier la présentation ou pour se conformer à de nouvelles exigences réglementaires.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait vérifier que cette consolidation est correctement expliquée dans le rapport et que les impacts sur les ratios de liquidité sont bien compris.</t>
+          <t>L'indicateur "Autres titres" a été ajouté dans le tableau de synthèse des actifs liquides par type et par monnaie au T2 2025, alors qu'il était absent au T1 2025.
+Cet ajout pourrait indiquer une nouvelle classification des actifs qui n'était pas précédemment divulguée de manière distincte. Les "autres titres" peuvent inclure des instruments financiers qui ne rentrent pas dans les catégories traditionnelles de titres de créance ou d'actions, et leur inclusion peut être motivée par des changements dans la stratégie d'investissement ou par des exigences de transparence accrues.
+Il s'agit probablement d'une mise à jour méthodologique ou d'une nouvelle divulgation. L'analyste devrait vérifier que cette nouvelle catégorie est correctement intégrée dans les rapports de liquidité et qu'elle respecte les normes de divulgation réglementaires.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1602,25 +1642,25 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Obligations de sociétés émettrices</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Comprennent les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Obligations de sociétés émettrices" a été retiré du tableau de synthèse des actifs liquides au T2 2025, alors qu'il était présent au T1 2025.
-Cette suppression pourrait être due à une réorganisation des catégories d'actifs, où ces obligations sont maintenant incluses dans une catégorie plus large ou différente. Cela peut refléter un changement dans la stratégie de gestion des actifs ou une réponse à des exigences réglementaires.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait s'assurer que cette modification est bien documentée et que les impacts sur les rapports financiers sont correctement évalués.</t>
+          <t>La note de bas de page n°2 a été ajoutée dans le tableau des actifs liquides par type et par monnaie au T2 2025. Cette note précise que les actifs incluent désormais les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.
+L'ajout de cette note indique une clarification ou une mise à jour de la composition des actifs liquides. Les titres adossés à des créances hypothécaires sont souvent soumis à des exigences de divulgation spécifiques en vertu des normes comptables et réglementaires, telles que Bâle III, qui impose des règles strictes sur la liquidité et la qualité des actifs. Cette inclusion pourrait refléter une révision de la méthodologie de classification des actifs ou une réponse à des exigences de transparence accrues.
+Il s'agit probablement d'une mise à jour méthodologique ou d'une nouvelle divulgation. L'analyste devrait confirmer que cette nouvelle catégorie est correctement intégrée dans les calculs de liquidité et qu'elle respecte les exigences réglementaires applicables.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1666,15 +1706,15 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Obligations du gouvernement des États-Unis</t>
+          <t>Obligations du gouvernement du Canada</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Obligations du gouvernement des États-Unis" a été retiré du tableau de synthèse des actifs liquides au T2 2025, alors qu'il était présent au T1 2025.
-Cette suppression semble être le résultat d'une consolidation des catégories d'obligations dans une nouvelle catégorie plus large, "Obligations du gouvernement, d’organismes fédéraux, d’entités du secteur public et de banques multilatérales de développement". Cela peut refléter un changement dans la manière dont la banque regroupe et rapporte ses actifs, potentiellement pour simplifier la présentation ou pour se conformer à de nouvelles exigences réglementaires.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait vérifier que cette consolidation est correctement expliquée dans le rapport et que les impacts sur les ratios de liquidité sont bien compris.</t>
+          <t>L'indicateur "Obligations du gouvernement du Canada" a été supprimé du tableau de synthèse des actifs liquides par type et par monnaie au T2 2025, alors qu'il était présent au T1 2025.
+Cette suppression pourrait indiquer une réorganisation des catégories d'actifs, où les obligations du gouvernement du Canada sont désormais incluses dans une catégorie plus large. Cela peut avoir des implications sur la manière dont la banque gère et rapporte ses actifs liquides, en particulier en ce qui concerne la conformité aux exigences de liquidité de Bâle III.
+Il s'agit probablement d'une mise à jour méthodologique. L'analyste devrait confirmer que cette suppression est compensée par une nouvelle classification appropriée et que les obligations du gouvernement du Canada sont toujours correctement prises en compte dans les rapports de liquidité.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1720,15 +1760,15 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Obligations d’agences fédérales des États-Unis, y compris leurs obligations adossées à des créances hypothécaires</t>
+          <t>Titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Obligations d’agences fédérales des États-Unis, y compris leurs obligations adossées à des créances hypothécaires" a été retiré du tableau de synthèse des actifs liquides au T2 2025, alors qu'il était présent au T1 2025.
-Cette suppression semble être le résultat d'une consolidation des catégories d'obligations dans une nouvelle catégorie plus large, "Obligations du gouvernement, d’organismes fédéraux, d’entités du secteur public et de banques multilatérales de développement". Cela peut refléter un changement dans la manière dont la banque regroupe et rapporte ses actifs, potentiellement pour simplifier la présentation ou pour se conformer à de nouvelles exigences réglementaires.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait vérifier que cette consolidation est correctement expliquée dans le rapport et que les impacts sur les ratios de liquidité sont bien compris.</t>
+          <t>L'indicateur "Titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation" a été supprimé du tableau de synthèse des actifs liquides par type et par monnaie au T2 2025, alors qu'il était présent au T1 2025.
+Cette suppression pourrait refléter un changement dans la manière dont ces titres sont classifiés ou rapportés. Les titres adossés à des créances hypothécaires sont souvent soumis à des exigences de divulgation spécifiques, et leur absence pourrait indiquer une révision de la méthodologie de classification ou une modification de la stratégie d'investissement.
+Il s'agit probablement d'une mise à jour méthodologique. L'analyste devrait s'assurer que ces titres sont toujours correctement pris en compte dans les rapports de liquidité et qu'ils respectent les normes de divulgation réglementaires.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1774,15 +1814,15 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Obligations d’autres entités souveraines, d’entités du secteur public et de banques multilatérales de développement (bloc 2)</t>
+          <t>Obligations de gouvernements provinciaux, d’entités du secteur public et de banques multilatérales de développement</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Obligations d’autres entités souveraines, d’entités du secteur public et de banques multilatérales de développement (bloc 2)" a été retiré du tableau de synthèse des actifs liquides au T2 2025, alors qu'il était présent au T1 2025.
-Cette suppression semble être le résultat d'une consolidation des catégories d'obligations dans une nouvelle catégorie plus large, "Obligations du gouvernement, d’organismes fédéraux, d’entités du secteur public et de banques multilatérales de développement". Cela peut refléter un changement dans la manière dont la banque regroupe et rapporte ses actifs, potentiellement pour simplifier la présentation ou pour se conformer à de nouvelles exigences réglementaires.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait vérifier que cette consolidation est correctement expliquée dans le rapport et que les impacts sur les ratios de liquidité sont bien compris.</t>
+          <t>L'indicateur "Obligations de gouvernements provinciaux, d’entités du secteur public et de banques multilatérales de développement" a été supprimé du tableau de synthèse des actifs liquides par type et par monnaie au T2 2025, alors qu'il était présent au T1 2025.
+Cette suppression pourrait indiquer une réorganisation des catégories d'actifs, où ces obligations sont désormais incluses dans une catégorie plus large. Cela peut avoir des implications sur la manière dont la banque gère et rapporte ses actifs liquides, en particulier en ce qui concerne la conformité aux exigences de liquidité de Bâle III.
+Il s'agit probablement d'une mise à jour méthodologique. L'analyste devrait confirmer que cette suppression est compensée par une nouvelle classification appropriée et que ces obligations sont toujours correctement prises en compte dans les rapports de liquidité.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1828,15 +1868,15 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Obligations de sociétés émettrices (bloc 2)</t>
+          <t>Obligations de sociétés émettrices</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Obligations de sociétés émettrices (bloc 2)" a été retiré du tableau de synthèse des actifs liquides au T2 2025, alors qu'il était présent au T1 2025.
-Cette suppression pourrait être due à une réorganisation des catégories d'actifs, où ces obligations sont maintenant incluses dans une catégorie plus large ou différente. Cela peut refléter un changement dans la stratégie de gestion des actifs ou une réponse à des exigences réglementaires.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait s'assurer que cette modification est bien documentée et que les impacts sur les rapports financiers sont correctement évalués.</t>
+          <t>L'indicateur "Obligations de sociétés émettrices" a été supprimé du tableau de synthèse des actifs liquides par type et par monnaie au T2 2025, alors qu'il était présent au T1 2025.
+Cette suppression pourrait indiquer une réorganisation des catégories d'actifs, où ces obligations sont désormais incluses dans une catégorie plus large ou sous une nouvelle dénomination. Cela peut avoir des implications sur la manière dont la banque gère et rapporte ses actifs liquides, en particulier en ce qui concerne la conformité aux exigences de liquidité de Bâle III.
+Il s'agit probablement d'une mise à jour méthodologique. L'analyste devrait confirmer que cette suppression est compensée par une nouvelle classification appropriée et que ces obligations sont toujours correctement prises en compte dans les rapports de liquidité.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1857,17 +1897,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1877,20 +1917,20 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Dépôts personnels</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Obligations du gouvernement des États-Unis</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Dépôts personnels" a été ajouté dans le tableau de synthèse du financement provenant des dépôts au T2 2025, alors qu'il était absent au T1 2025.
-Cet ajout semble indiquer une nouvelle catégorisation des dépôts, séparant les dépôts personnels des dépôts non personnels. Cela pourrait refléter un changement dans la manière dont la banque souhaite présenter ses sources de financement, potentiellement pour mieux aligner ses rapports avec les exigences réglementaires ou pour améliorer la transparence envers les parties prenantes.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait confirmer que cette nouvelle catégorisation est cohérente avec d'autres sections du rapport et qu'elle ne modifie pas les ratios prudentiels ou les exigences de divulgation.</t>
+          <t>L'indicateur "Obligations du gouvernement des États-Unis" a été supprimé du tableau de synthèse des actifs liquides par type et par monnaie au T2 2025, alors qu'il était présent au T1 2025.
+Cette suppression pourrait indiquer une réorganisation des catégories d'actifs, où ces obligations sont désormais incluses dans une catégorie plus large. Cela peut avoir des implications sur la manière dont la banque gère et rapporte ses actifs liquides, en particulier en ce qui concerne la conformité aux exigences de liquidité de Bâle III.
+Il s'agit probablement d'une mise à jour méthodologique. L'analyste devrait confirmer que cette suppression est compensée par une nouvelle classification appropriée et que ces obligations sont toujours correctement prises en compte dans les rapports de liquidité.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1899,21 +1939,9 @@
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-19T00:09:15.437204+00:00</t>
-        </is>
-      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1923,17 +1951,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1943,20 +1971,20 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Dépôts non personnels</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Obligations d’agences fédérales des États-Unis, y compris leurs obligations adossées à des créances hypothécaires</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Dépôts non personnels" a été ajouté dans le tableau de synthèse du financement provenant des dépôts au T2 2025, alors qu'il était absent au T1 2025.
-Cet ajout indique une nouvelle approche dans la présentation des dépôts, séparant les dépôts non personnels des dépôts personnels. Cela pourrait être motivé par un besoin de conformité réglementaire ou par une volonté d'améliorer la clarté des informations fournies aux investisseurs et aux régulateurs.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait vérifier que cette nouvelle présentation est alignée avec les autres sections du rapport et qu'elle respecte les normes de divulgation en vigueur.</t>
+          <t>L'indicateur "Obligations d’agences fédérales des États-Unis, y compris leurs obligations adossées à des créances hypothécaires" a été supprimé du tableau de synthèse des actifs liquides par type et par monnaie au T2 2025, alors qu'il était présent au T1 2025.
+Cette suppression pourrait indiquer une réorganisation des catégories d'actifs, où ces obligations sont désormais incluses dans une catégorie plus large. Cela peut avoir des implications sur la manière dont la banque gère et rapporte ses actifs liquides, en particulier en ce qui concerne la conformité aux exigences de liquidité de Bâle III.
+Il s'agit probablement d'une mise à jour méthodologique. L'analyste devrait confirmer que cette suppression est compensée par une nouvelle classification appropriée et que ces obligations sont toujours correctement prises en compte dans les rapports de liquidité.</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1977,44 +2005,40 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES PAR TYPE ET PAR MONNAIE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Les dépôts personnels et commerciaux aux États-Unis sont présentés selon un équivalent en dollars canadiens, par conséquent les variations d’une période à l’autre reflètent la croissance sous-jacente et la variation du taux de change.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>La méthode de calcul a été modifiée pour tenir compte du financement provenant des dépôts généré par les services bancaires personnels et commerciaux et les activités de gestion de patrimoine.</t>
-        </is>
-      </c>
+          <t>Obligations d’autres entités souveraines, d’entités du secteur public et de banques multilatérales de développement</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n°1 a subi une révision significative dans le tableau du financement provenant des dépôts entre le T1 2025 et le T2 2025. Initialement, elle expliquait que les dépôts personnels et commerciaux aux États-Unis étaient convertis en dollars canadiens, reflétant ainsi les variations de change et la croissance sous-jacente. Désormais, elle indique que la méthode de calcul a été modifiée pour inclure le financement généré par les services bancaires personnels et commerciaux ainsi que les activités de gestion de patrimoine.
-Ce changement a un impact structurel important, car il modifie la manière dont les dépôts sont comptabilisés et présentés. Cela pourrait avoir des implications sur les ratios financiers et la manière dont la banque est perçue par les régulateurs et les investisseurs. En particulier, l'inclusion des activités de gestion de patrimoine dans le calcul des dépôts pourrait affecter les ratios de liquidité et de capital, qui sont des éléments clés des exigences de Bâle III et des lignes directrices du BSIF.
-Il s'agit d'une mise à jour méthodologique significative. L'analyste devrait investiguer pour s'assurer que cette nouvelle méthode de calcul est cohérente avec les autres sections du rapport et qu'elle respecte les normes de divulgation en vigueur. Il est recommandé de vérifier si cette modification a été communiquée de manière adéquate aux parties prenantes et si elle est alignée avec les pratiques de l'industrie.</t>
+          <t>L'indicateur "Obligations d’autres entités souveraines, d’entités du secteur public et de banques multilatérales de développement" a été supprimé du tableau de synthèse des actifs liquides par type et par monnaie au T2 2025, alors qu'il était présent au T1 2025.
+Cette suppression pourrait indiquer une réorganisation des catégories d'actifs, où ces obligations sont désormais incluses dans une catégorie plus large. Cela peut avoir des implications sur la manière dont la banque gère et rapporte ses actifs liquides, en particulier en ce qui concerne la conformité aux exigences de liquidité de Bâle III.
+Il s'agit probablement d'une mise à jour méthodologique. L'analyste devrait confirmer que cette suppression est compensée par une nouvelle classification appropriée et que ces obligations sont toujours correctement prises en compte dans les rapports de liquidité.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2055,20 +2079,20 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Dépôts personnels et commerciaux – au Canada</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Dépôts personnels</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Dépôts personnels et commerciaux – au Canada" a été supprimé du tableau de synthèse du financement provenant des dépôts au T2 2025, alors qu'il était présent au T1 2025.
-Cette suppression suggère une réorganisation des catégories de dépôts, potentiellement pour mieux distinguer les dépôts personnels des dépôts non personnels. Cela pourrait être lié à une révision des pratiques de divulgation pour se conformer aux nouvelles normes ou pour améliorer la transparence des rapports financiers.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait s'assurer que cette suppression n'affecte pas la compréhension globale des sources de financement et qu'elle est cohérente avec les autres sections du rapport.</t>
+          <t>L'indicateur "Dépôts personnels" a été ajouté dans le tableau de synthèse du financement provenant des dépôts au T2 2025, alors qu'il n'était pas présent au T1 2025.
+Cet ajout pourrait refléter une nouvelle segmentation des dépôts, ce qui peut avoir un impact sur la manière dont la banque gère et rapporte ses sources de financement. Une telle segmentation peut être liée à des exigences de divulgation plus détaillées ou à une stratégie interne visant à mieux comprendre la composition des dépôts.
+Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait vérifier si cette nouvelle catégorie est alignée avec d'autres rapports financiers et si elle répond à des exigences réglementaires spécifiques.</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2077,9 +2101,21 @@
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23T09:36:43.635454+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2109,20 +2145,20 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Dépôts personnels et commerciaux – aux États-Unis¹</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Dépôts non personnels</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Dépôts personnels et commerciaux – aux États-Unis¹" a été supprimé du tableau de synthèse du financement provenant des dépôts au T2 2025, alors qu'il était présent au T1 2025.
-Cette suppression pourrait indiquer une révision de la manière dont les dépôts sont catégorisés, potentiellement pour mieux aligner les rapports avec les exigences réglementaires ou pour clarifier la présentation des données financières. Cela pourrait également refléter un changement dans la stratégie de financement de la banque.
-Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait vérifier que cette suppression est cohérente avec les autres sections du rapport et qu'elle ne compromet pas la transparence des informations fournies aux parties prenantes.</t>
+          <t>L'indicateur "Dépôts non personnels" a été ajouté dans le tableau de synthèse du financement provenant des dépôts au T2 2025, alors qu'il n'était pas présent au T1 2025.
+Cet ajout suggère une nouvelle classification des dépôts, potentiellement pour distinguer les dépôts institutionnels ou d'entreprise des dépôts individuels. Cela peut avoir des implications sur la gestion des risques et la stratégie de liquidité de la banque, en particulier si ces dépôts sont soumis à des conditions ou des risques différents.
+Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait confirmer que cette distinction est cohérente avec les pratiques de l'industrie et qu'elle est correctement intégrée dans les systèmes de gestion des risques de la banque.</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2138,45 +2174,49 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>STRUCTURE DE FONDS PROPRES ET RATIOS – Bâle III</t>
+          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Les dépôts personnels et commerciaux aux États-Unis sont présentés selon un équivalent en dollars canadiens, par conséquent les variations d’une période à l’autre reflètent la croissance sous-jacente et la variation du taux de change.</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Ajustements de valorisation prudentiels</t>
+          <t>La méthode de calcul a été modifiée pour tenir compte du financement provenant des dépôts généré par les services bancaires personnels et commerciaux et les activités de gestion de patrimoine.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Ajustements de valorisation prudentiels" a été ajouté dans le tableau de gestion du capital au T2 2025, alors qu'il était absent au T1 2025.
-Cet ajout peut refléter une nouvelle exigence de divulgation ou une mise à jour des pratiques comptables en matière de valorisation des actifs. Les ajustements de valorisation prudentiels sont cruciaux pour s'assurer que les actifs sont évalués de manière conservatrice, ce qui est essentiel pour le calcul des fonds propres réglementaires selon les normes de Bâle III.
-Il s'agit probablement d'une mise à jour méthodologique ou d'une nouvelle divulgation structurelle. L'analyste devrait confirmer que cet ajout est conforme aux nouvelles directives réglementaires ou aux pratiques de l'industrie.</t>
+          <t>La note de bas de page n°1 a subi une révision significative dans le tableau du sommaire du financement provenant des dépôts. Initialement, elle expliquait que les dépôts personnels et commerciaux aux États-Unis étaient convertis en dollars canadiens, reflétant ainsi les variations de change et la croissance sous-jacente. Désormais, elle indique que la méthode de calcul a été modifiée pour inclure le financement provenant des dépôts généré par les services bancaires personnels et commerciaux ainsi que les activités de gestion de patrimoine.
+Ce changement a un impact important sur la manière dont les dépôts sont comptabilisés et présentés. En intégrant les activités de gestion de patrimoine, la banque élargit potentiellement la base de ses dépôts, ce qui peut influencer les ratios de liquidité et de financement, des éléments cruciaux sous les normes de Bâle III. De plus, cette modification pourrait répondre à des exigences de divulgation plus strictes imposées par le BSIF ou d'autres régulateurs, visant à améliorer la transparence des sources de financement.
+Il s'agit d'une mise à jour structurelle et méthodologique du tableau. L'analyste devrait confirmer que cette nouvelle méthode de calcul est cohérente avec les autres pratiques de reporting de la banque et qu'elle est correctement intégrée dans les systèmes de gestion des risques. Une vérification de la conformité avec les normes réglementaires en vigueur est également recommandée.</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2192,49 +2232,45 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE</t>
+          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>En plus des expositions présentées ci-dessus, la Banque a également une exposition de 35,3 milliards de dollars (35,5 milliards de dollars au 31 octobre 2024) à des entités supranationales.</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>En plus des expositions présentées ci-dessus, la Banque a également une exposition de 33,6 milliards de dollars (35,5 milliards de dollars au 31 octobre 2024) à des entités supranationales.</t>
-        </is>
-      </c>
+          <t>Dépôts personnels et commerciaux – au Canada</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n°4 a été modifiée dans le tableau de l'exposition nette par région et contrepartie. Le texte a été révisé pour indiquer que l'exposition de la Banque à des entités supranationales est passée de 35,3 milliards de dollars à 33,6 milliards de dollars.
-Ce changement est significatif car il reflète une variation dans l'exposition financière de la Banque à des entités supranationales, ce qui peut avoir des implications sur les ratios de capital et la gestion des risques. Une telle modification pourrait être liée à des ajustements dans la stratégie d'investissement ou à des changements dans les conditions de marché. Selon les normes de Bâle III, les expositions à des entités supranationales peuvent influencer les exigences de fonds propres, et toute variation doit être soigneusement analysée pour évaluer son impact sur la solidité financière de l'institution.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer la raison de cette réduction d'exposition et s'assurer qu'elle est cohérente avec les autres divulgations financières de la Banque. Une vérification supplémentaire pourrait être nécessaire pour comprendre les implications de ce changement sur la gestion des risques et la conformité réglementaire.</t>
+          <t>L'indicateur "Dépôts personnels et commerciaux – au Canada" a été retiré du tableau de synthèse du financement provenant des dépôts au T2 2025, alors qu'il était présent au T1 2025.
+La suppression de cet indicateur peut indiquer un changement dans la manière dont la banque regroupe ou rapporte ses dépôts. Cela pourrait être dû à une réorganisation interne des catégories de dépôts ou à une nouvelle approche de reporting qui ne nécessite plus cette distinction spécifique.
+Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait examiner si cette suppression est compensée par d'autres indicateurs ou si elle reflète un changement dans la stratégie de gestion des dépôts de la banque.</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2248,190 +2284,182 @@
       <c r="N31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>(sans titre)</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS¹</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Dépôts personnels et commerciaux – aux États-Unis¹</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>L'indicateur "Dépôts personnels et commerciaux – aux États-Unis¹" a été retiré du tableau de synthèse du financement provenant des dépôts au T2 2025, alors qu'il était présent au T1 2025.
+Cette suppression pourrait signaler un changement dans la manière dont la banque segmente ou rapporte ses dépôts transfrontaliers. Cela peut avoir des implications sur la gestion des risques de change ou sur la stratégie de financement international de la banque.
+Il s'agit d'une mise à jour structurelle du tableau. L'analyste devrait vérifier si cette suppression est justifiée par une nouvelle méthodologie de reporting ou si elle nécessite une révision des pratiques de gestion des dépôts internationaux.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>STRUCTURE DE FONDS PROPRES ET RATIOS – Bâle III</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Ajustements de valorisation prudentiels</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>L'indicateur "Ajustements de valorisation prudentiels" a été ajouté dans le tableau de gestion du capital au T2 2025, alors qu'il était absent au T1 2025.
+Cet ajout peut refléter une nouvelle exigence de divulgation ou une mise à jour des pratiques comptables pour mieux aligner les rapports financiers avec les normes prudentielles. Les ajustements de valorisation prudentiels sont souvent liés à la gestion des risques de marché et à la transparence des états financiers, ce qui est crucial pour les parties prenantes et les régulateurs.
+Il s'agit probablement d'une mise à jour structurelle importante. L'analyste devrait confirmer que cet ajout est conforme aux nouvelles directives réglementaires ou aux changements de méthodologie de l'institution.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Modification</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Le LCR est calculé conformément à la ligne directrice Normes de liquidité du BSIF, qui tient compte des exigences en matière de liquidité publiées par le CBCB. Le LCR pour le trimestre clos le 31 janvier 2025 représente la moyenne des 62 données quotidiennes du trimestre.</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Le LCR est calculé conformément à la ligne directrice Normes de liquidité du BSIF, qui tient compte des exigences en matière de liquidité publiées par le CBCB. Le LCR pour le trimestre clos le 30 avril 2025 représente la moyenne des 61 données quotidiennes du trimestre.</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>La note de bas de page n-1 a été modifiée dans le tableau des mesures de liquidité réglementaire de la Banque au T2 2025.
-La modification concerne le nombre de données quotidiennes utilisées pour calculer la moyenne du LCR, passant de 62 à 61. Ce changement est purement technique et reflète une mise à jour du nombre de jours dans le trimestre, ce qui est une pratique courante et attendue dans le cadre des rapports trimestriels.
-Il s'agit d'une mise à jour ordinaire qui n'affecte pas la méthodologie de calcul du LCR. L'analyste peut confirmer cette mise à jour sans nécessiter d'investigation supplémentaire, car elle ne modifie pas les principes sous-jacents du calcul du ratio.</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="3" t="inlineStr"/>
-      <c r="M32" s="3" t="inlineStr"/>
-      <c r="N32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>ACTIFS GREVÉS ET ACTIFS NON GREVÉS</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Représentent les actifs qui sont disponibles facilement pour être utilisés en tant que sûreté afin d’obtenir du financement ou de satisfaire aux exigences en matière de garantie. Cette catégorie comprend les prêts non grevés adossés à des biens immobiliers qui sont admissibles à titre de garantie à la FHLB.</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Représentent les actifs qui sont disponibles facilement pour être utilisés en tant que sûreté afin d’obtenir du financement ou de satisfaire aux exigences en matière de garantie. Cette catégorie comprend les prêts non grevés adossés à des biens immobiliers qui sont admissibles à titre de garantie à la Federal Home Loan Bank (FHLB).</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>La note de bas de page n-3 a été modifiée pour clarifier l'acronyme FHLB en son nom complet 'Federal Home Loan Bank'. Cette modification se trouve dans le tableau des actifs grevés et non grevés, et concerne la description des actifs disponibles comme garantie.
-L'impact métier de cette clarification est principalement cosmétique, car elle n'affecte pas la méthodologie de calcul ou les exigences réglementaires. Cependant, elle améliore la compréhension pour les lecteurs qui ne seraient pas familiers avec l'acronyme. Les exigences de divulgation selon Bâle III ou les lignes directrices du BSIF ne sont pas directement touchées par cette clarification.
-Il s'agit d'une mise à jour ordinaire visant à améliorer la clarté du document. L'analyste peut confirmer que cette clarification n'introduit pas de nouvelles interprétations ou obligations réglementaires.</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>En plus des expositions présentées ci-dessus, la Banque a également une exposition de 35,3 milliards de dollars (35,5 milliards de dollars au 31 octobre 2024) à des entités supranationales.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>En plus des expositions présentées ci-dessus, la Banque a également une exposition de 33,6 milliards de dollars (35,5 milliards de dollars au 31 octobre 2024) à des entités supranationales.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>La note de bas de page n°4 a été modifiée dans le tableau de l'exposition nette par région et contrepartie. Le texte a été révisé pour indiquer que l'exposition de la Banque à des entités supranationales est passée de 35,3 milliards de dollars à 33,6 milliards de dollars.
+Ce changement a un impact direct sur la divulgation des expositions de la Banque, ce qui est crucial pour l'évaluation des risques et la conformité réglementaire. Une telle modification peut influencer les ratios prudentiels et la perception du risque par les régulateurs et les investisseurs. Selon les normes de Bâle III, les expositions à des entités supranationales peuvent affecter le calcul des actifs pondérés en fonction des risques (RWA), ce qui a des implications sur le ratio de fonds propres.
+Il s'agit d'une mise à jour significative des données financières qui nécessite une vérification approfondie. L'analyste devrait confirmer l'exactitude de cette nouvelle valeur et s'assurer qu'elle est cohérente avec les autres divulgations financières du rapport. Une investigation plus poussée pourrait être nécessaire pour comprendre les raisons de cette variation.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>Validé</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>analyst</t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-19T00:10:03.581509+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>DURÉE CONTRACTUELLE RESTANTE</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Comprennent 633 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Comprennent 653 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>La note de bas de page n°6 a été modifiée pour refléter une augmentation des engagements de crédit à l'égard de placements dans des actions de sociétés à capital fermé, passant de 633 millions de dollars à 653 millions de dollars. Ce changement est relativement mineur en termes de montant, mais il peut indiquer une légère augmentation de l'exposition de la banque à ce type d'investissement.
-Bien que l'impact sur les ratios prudentiels globaux soit probablement limité, cette modification pourrait signaler une stratégie d'investissement plus agressive ou une opportunité d'investissement spécifique identifiée par la banque. Les engagements de crédit envers des sociétés à capital fermé peuvent comporter des risques accrus, et il est important de surveiller ces engagements dans le contexte des exigences de fonds propres de Bâle III.
-Ce changement constitue une mise à jour ordinaire des chiffres financiers. L'analyste devrait vérifier que cette augmentation est cohérente avec les autres informations financières fournies dans le rapport et s'assurer qu'elle ne modifie pas de manière significative le profil de risque global de la banque.</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr"/>
-      <c r="L34" s="3" t="inlineStr"/>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23T09:37:35.651984+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -2441,17 +2469,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS NON GREVÉS DÉTENUS PAR LA BANQUE, LES FILIALES ET LES SUCCURSALES</t>
+          <t>(sans titre)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2461,18 +2489,24 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Le LCR est calculé conformément à la ligne directrice Normes de liquidité du BSIF, qui tient compte des exigences en matière de liquidité publiées par le CBCB. Le LCR pour le trimestre clos le 31 janvier 2025 représente la moyenne des 62 données quotidiennes du trimestre.</t>
+        </is>
+      </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Comprennent les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.</t>
+          <t>Le LCR est calculé conformément à la ligne directrice Normes de liquidité du BSIF, qui tient compte des exigences en matière de liquidité publiées par le CBCB. Le LCR pour le trimestre clos le 30 avril 2025 représente la moyenne des 61 données quotidiennes du trimestre.</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>L'ajout d'une nouvelle note de bas de page sans contexte détaillé nécessite une vérification manuelle pour confirmer son impact.</t>
+          <t>La note de bas de page n°1 a été modifiée dans le tableau des mesures de liquidité réglementaires et notes explicatives au T2 2025. Le texte a été mis à jour pour refléter le changement dans le nombre de données quotidiennes utilisées pour calculer le LCR, passant de 62 à 61.
+Ce changement est principalement technique et reflète une mise à jour mineure dans la méthodologie de calcul du LCR, qui est une mesure clé de la liquidité à court terme. Le LCR est calculé conformément aux normes de Bâle III et aux lignes directrices du BSIF, et cette mise à jour n'affecte pas la compréhension globale de la mesure, mais elle assure la précision des calculs.
+Il s'agit d'une mise à jour ordinaire qui n'a pas d'impact significatif sur la divulgation ou la compréhension des risques de liquidité. L'analyste peut confirmer cette mise à jour comme une correction technique et s'assurer que les calculs sont correctement appliqués dans le contexte des exigences réglementaires.</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2488,39 +2522,49 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>INDICATEURS BISM¹</t>
+          <t>DURÉE CONTRACTUELLE RESTANTE</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr"/>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>INDICATEURS BISM¹</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr"/>
+          <t>Comprennent 633 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Comprennent 653 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
+        </is>
+      </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Tableau supprimé du trimestre courant.</t>
+          <t>La note de bas de page n°6 a été modifiée pour refléter une augmentation des engagements de crédit à l'égard de placements dans des actions de sociétés à capital fermé, passant de 633 millions de dollars à 653 millions de dollars. Cette modification est présente dans le tableau des engagements hors bilan.
+Bien que l'augmentation de 20 millions de dollars puisse sembler mineure en termes absolus, elle peut indiquer une stratégie d'investissement plus agressive ou une réévaluation des engagements existants. Les engagements de crédit envers des sociétés à capital fermé peuvent comporter des risques accrus en raison de la nature moins liquide et plus spéculative de ces investissements. Toutefois, cette modification n'a pas d'impact direct sur les ratios prudentiels ou les exigences de fonds propres selon les normes de Bâle III, car elle concerne des engagements hors bilan.
+Il s'agit d'une mise à jour ordinaire qui ne nécessite pas d'action immédiate, mais l'analyste devrait surveiller les tendances de ces engagements dans les prochains rapports pour détecter tout changement significatif dans la stratégie d'investissement de la banque. Une attention particulière pourrait être portée à l'évolution de ces engagements dans le contexte des conditions de marché.</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2533,8 +2577,174 @@
       <c r="M36" s="3" t="inlineStr"/>
       <c r="N36" s="3" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>NOTATIONS DE CRÉDIT¹</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Perspectives – Stables (court terme)</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>L'indicateur 'Perspectives – Stables (court terme)' a été retiré du tableau des notations de crédit au T2 2025, alors qu'il était présent au T1 2025.
+Cet indicateur fournissait une indication sur la stabilité des perspectives à court terme, ce qui peut être pertinent pour les investisseurs et les analystes évaluant la solidité financière à court terme de l'institution. Cependant, son absence n'affecte pas directement les exigences réglementaires telles que Bâle III ou les lignes directrices du BSIF, car il s'agit d'une information plus qualitative que quantitative.
+Il s'agit probablement d'une mise à jour ordinaire du tableau, visant à simplifier la présentation des perspectives. L'analyste devrait confirmer que cette suppression n'entraîne pas de perte d'information critique pour les parties prenantes.</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-23T09:37:09.460310+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS NON GREVÉS DÉTENUS PAR LA BANQUE, LES FILIALES ET LES SUCCURSALES</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Comprennent les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>L'ajout d'une nouvelle note de bas de page sans contexte détaillé nécessite une vérification manuelle pour confirmer son impact.</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
+      <c r="M38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>INDICATEURS BISM¹</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>INDICATEURS BISM¹</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N36"/>
+  <autoFilter ref="A1:N39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/resultats/td/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/td/2025_t2_vs_2025_t1/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$M$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -460,11 +460,10 @@
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,7 +514,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Nouvelle divulgation ?</t>
+          <t>Nouvelle idée ?</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -529,11 +528,6 @@
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Validé par</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Validé le</t>
         </is>
@@ -591,7 +585,6 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -647,21 +640,8 @@
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-23T09:36:50.293551+00:00</t>
-        </is>
-      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -715,7 +695,6 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -771,21 +750,8 @@
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-23T09:38:13.252037+00:00</t>
-        </is>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -841,21 +807,8 @@
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-23T09:37:32.461532+00:00</t>
-        </is>
-      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -911,21 +864,8 @@
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-23T09:37:13.014781+00:00</t>
-        </is>
-      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -983,7 +923,6 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1037,7 +976,6 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1093,21 +1031,8 @@
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-23T09:38:07.654009+00:00</t>
-        </is>
-      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1159,21 +1084,8 @@
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-23T09:36:37.996258+00:00</t>
-        </is>
-      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1227,7 +1139,6 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1281,7 +1192,6 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1335,7 +1245,6 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1389,7 +1298,6 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1443,7 +1351,6 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1497,7 +1404,6 @@
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1556,12 +1462,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-23T09:35:55.816120+00:00</t>
+          <t>2026-05-15T01:26:44.297625+00:00</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1518,6 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1671,7 +1571,6 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1725,7 +1624,6 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1779,7 +1677,6 @@
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1833,7 +1730,6 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1887,7 +1783,6 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1941,7 +1836,6 @@
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1995,7 +1889,6 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2049,7 +1942,6 @@
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2101,21 +1993,8 @@
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-23T09:36:43.635454+00:00</t>
-        </is>
-      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2169,7 +2048,6 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2227,7 +2105,6 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2281,7 +2158,6 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2335,7 +2211,6 @@
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2389,7 +2264,6 @@
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2445,21 +2319,8 @@
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-23T09:37:35.651984+00:00</t>
-        </is>
-      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -2517,7 +2378,6 @@
       <c r="K35" s="3" t="inlineStr"/>
       <c r="L35" s="3" t="inlineStr"/>
       <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -2575,7 +2435,6 @@
       <c r="K36" s="3" t="inlineStr"/>
       <c r="L36" s="3" t="inlineStr"/>
       <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -2627,21 +2486,8 @@
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr"/>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-23T09:37:09.460310+00:00</t>
-        </is>
-      </c>
+      <c r="L37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -2693,7 +2539,6 @@
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="inlineStr"/>
       <c r="M38" s="3" t="inlineStr"/>
-      <c r="N38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2741,10 +2586,9 @@
       <c r="K39" s="3" t="inlineStr"/>
       <c r="L39" s="3" t="inlineStr"/>
       <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N39"/>
+  <autoFilter ref="A1:M39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>